--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:34</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
@@ -36,30 +36,30 @@
     <t xml:space="preserve">Antofagasta</t>
   </si>
   <si>
+    <t xml:space="preserve">Mejillones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ollagüe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taltal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tocopilla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">María Elena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Pedro de Atacama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calama</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sierra Gorda</t>
   </si>
   <si>
-    <t xml:space="preserve">San Pedro de Atacama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ollagüe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mejillones</t>
-  </si>
-  <si>
-    <t xml:space="preserve">María Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taltal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tocopilla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calama</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -499,13 +499,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.4</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="3">
@@ -516,13 +516,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2203</v>
+        <v>2202</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.74</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="4">
@@ -533,13 +533,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2202</v>
+        <v>2104</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.24</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="5">
@@ -550,13 +550,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2102</v>
+        <v>2301</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1.5</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="7">
@@ -584,13 +584,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2104</v>
+        <v>2203</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-2.57</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-2.61</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="9">
@@ -618,13 +618,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2301</v>
+        <v>2201</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-5.63</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="10">
@@ -635,13 +635,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>2201</v>
+        <v>2103</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-6.34</v>
+        <v>-6.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:29</t>
+    <t xml:space="preserve">2026-09-27 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.54</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.02</v>
+        <v>20.2</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.66</v>
+        <v>16.62</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.35</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.62</v>
+        <v>-6.23</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.73</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.76</v>
+        <v>-7.58</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1.35</v>
+        <v>-13.53</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-6.8</v>
+        <v>-67.96</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:11</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:25</t>
+    <t xml:space="preserve">2026-10-05 08:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
